--- a/AAII_Financials/Quarterly/XYZ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/XYZ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
   <si>
     <t>XYZ</t>
   </si>
@@ -656,212 +656,225 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6617700</v>
+      </c>
+      <c r="E8" s="3">
         <v>6056800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6252500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6115000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6054500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5771800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>6032600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5975800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6155600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5957100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5773000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5617500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5535000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4990100</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3438800</v>
+      </c>
+      <c r="E9" s="3">
         <v>3134800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3366300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3439500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3503500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3467500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3705600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3708900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3904500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3844600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3729200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3701200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3650500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3257000</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3178900</v>
+      </c>
+      <c r="E10" s="3">
         <v>2922100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2886100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2675400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2550900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2304300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2327000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2266900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2251100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2112500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2043800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1916300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1884500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1733100</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -878,52 +891,56 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>608700</v>
+      </c>
+      <c r="E12" s="3">
         <v>1038900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>710700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>711200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>725300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>760700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>769700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>711000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>713200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>720600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>685400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>713800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>694700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>626900</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -966,96 +983,105 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E14" s="3">
         <v>5700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-171100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-1600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>40800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>3000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-3600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>132000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>14900</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>47100</v>
+      </c>
+      <c r="E15" s="3">
         <v>47000</v>
-      </c>
-      <c r="E15" s="3">
-        <v>48000</v>
       </c>
       <c r="F15" s="3">
         <v>48000</v>
       </c>
       <c r="G15" s="3">
-        <v>48300</v>
+        <v>48000</v>
       </c>
       <c r="H15" s="3">
         <v>48300</v>
       </c>
       <c r="I15" s="3">
+        <v>48300</v>
+      </c>
+      <c r="J15" s="3">
         <v>50200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>53200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>58400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>61300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>61200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>74800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>55300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>55600</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1069,96 +1095,103 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>6154500</v>
+      </c>
+      <c r="E17" s="3">
         <v>6216200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5754200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5694800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5559300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5427600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5926300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5636400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5832900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5687700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5749900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5611400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5653400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4996300</v>
       </c>
     </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>463200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-159400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>498300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>420100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>495200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>344200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>106200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>339400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>322700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>269400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>23200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>6100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-118400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-6200</v>
       </c>
     </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1175,228 +1208,244 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>85500</v>
+      </c>
+      <c r="E20" s="3">
         <v>161700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>229300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-55600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-197200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>84900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-248200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-17900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>63100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-238900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-133700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>23300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-16000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-92600</v>
       </c>
     </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>424700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-274100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>316900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>523700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>740700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>307600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>404600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>410500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>317900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>569700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>218100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>57600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-47100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>142000</v>
       </c>
     </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>94400</v>
+      </c>
+      <c r="E22" s="3">
         <v>92300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>108800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>74500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>59300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>63300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>85700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>65200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>50700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>35800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>51700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>32300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>30100</v>
       </c>
-      <c r="P22" s="3" t="s">
+      <c r="Q22" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>301500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-392600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>202000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>601500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>659400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>227100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>277800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>324100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>248900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>506300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>22100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-12400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-113500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>74700</v>
       </c>
     </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>214400</v>
+      </c>
+      <c r="E24" s="3">
         <v>-84000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>86400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>139900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>121000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>38300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1646900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>43000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>59000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>35500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-59900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>81100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-8200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-21100</v>
       </c>
     </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1439,96 +1488,105 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>87100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-308600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>115600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>461600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>538300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>188700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1924700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>281100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>189900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>470800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>82000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-93500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-105400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>95800</v>
       </c>
     </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>88500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-308700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>115800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>461500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>538500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>189900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1946000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>283800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>195300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>472000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>102200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-88700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-102000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>98300</v>
       </c>
     </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1571,8 +1629,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1615,8 +1676,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1659,8 +1723,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1703,96 +1770,105 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-85500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-161700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-229300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>55600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>197200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-84900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>248200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>17900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-63100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>238900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>133700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-23300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>16000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>92600</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>88500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-308700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>115800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>461500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>538500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>189900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1946000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>283800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>195300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>472000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>102200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-88700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-102000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>98300</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1835,101 +1911,110 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>88500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-308700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>115800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>461500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>538500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>189900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1946000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>283800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>195300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>472000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>102200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-88700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-102000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>98300</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1946,8 +2031,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1964,404 +2050,432 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6427300</v>
+      </c>
+      <c r="E41" s="3">
         <v>6858400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6564100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8335900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6384200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7088800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8075200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>8299800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7799100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5753400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4996500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5112300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4745900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5061100</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>310800</v>
+      </c>
+      <c r="E42" s="3">
         <v>462600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>628000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>448900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>397400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>427100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>491400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>562200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>696500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>614800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1249500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1161100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1121800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1024100</v>
       </c>
     </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8291400</v>
+      </c>
+      <c r="E43" s="3">
         <v>7761900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8099900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6123400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5060400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4177600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4558600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4476200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6768100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6420500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6418600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6124900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4389400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4002100</v>
       </c>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>198900</v>
+      </c>
+      <c r="E44" s="3">
         <v>174300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>158300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>166600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>138100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>108800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>105000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>118100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>104700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>119400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>110100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>96400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>97900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>101700</v>
       </c>
     </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6073900</v>
+      </c>
+      <c r="E45" s="3">
         <v>6782800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5263300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5324900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5314700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5628900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4507100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5572300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5225100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5952100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3397400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3764300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4309800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4684800</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>23144900</v>
+      </c>
+      <c r="E46" s="3">
         <v>23766400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>22856900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>22067700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>19707700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>19712400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>19880200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>20774900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>22291300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>20538300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>17818700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>17540600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>15841100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>15900500</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>328800</v>
+      </c>
+      <c r="E47" s="3">
         <v>242700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>612100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>595000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>443100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>516700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>717500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>643700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>575100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>397400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>456400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>631300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>502400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>618000</v>
       </c>
     </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>428300</v>
+      </c>
+      <c r="E48" s="3">
         <v>483300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>538300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>557200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>513400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>521300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>534400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>549500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>528600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>533600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>540800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>585300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>610700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>676400</v>
       </c>
     </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>13167300</v>
+      </c>
+      <c r="E49" s="3">
         <v>13202000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>13130700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>13133900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>13185500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>12895000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>12850500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>13656000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>13451400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>13394900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>13681200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>13528100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>13822300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>13868400</v>
       </c>
     </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2404,8 +2518,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2448,52 +2565,58 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>825900</v>
+      </c>
+      <c r="E52" s="3">
         <v>910900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1109200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1286600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1214800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>984100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>994000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>731200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>700200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>748600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>524800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>269500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>299400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>274100</v>
       </c>
     </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2536,52 +2659,58 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>39156700</v>
+      </c>
+      <c r="E54" s="3">
         <v>39986100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>39549900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>39182800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>36858400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>36395600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>36777600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>36355400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>37546600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>35612800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>33031300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>32554900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>31075900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>31337300</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2598,8 +2727,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2616,272 +2746,291 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>122400</v>
+      </c>
+      <c r="E57" s="3">
         <v>134000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>114600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>125900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>118800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>89000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>118000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>94200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>112700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>91400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>142600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>139800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>89600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>100100</v>
       </c>
     </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>633500</v>
+      </c>
+      <c r="E58" s="3">
         <v>1914000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2095600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1784900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1743000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>52000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1237400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1190400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1513900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1460800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>806800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>104700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>587900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>828400</v>
       </c>
     </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8986900</v>
+      </c>
+      <c r="E59" s="3">
         <v>8531100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7453700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7462800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7590600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7736900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6408500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>8124100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>10130100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10406000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7332800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>8445300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7088100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>7340000</v>
       </c>
     </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>10478500</v>
+      </c>
+      <c r="E60" s="3">
         <v>11967100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>10384500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10108000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10071300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8686700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8546800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10040000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>12230700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>12501200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8883000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>9192100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8239000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8706300</v>
       </c>
     </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6537800</v>
+      </c>
+      <c r="E61" s="3">
         <v>6219400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6870800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6316500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4379500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5992900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6681200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6218800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5855200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3951000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5264800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5278800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4719900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4826600</v>
       </c>
     </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>119500</v>
+      </c>
+      <c r="E62" s="3">
         <v>118500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>123500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>122800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>121900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>118100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>152200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>146400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>130700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>166000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>155000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>253500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>347200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>329600</v>
       </c>
     </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2924,8 +3073,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2968,8 +3120,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3012,52 +3167,58 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>17145400</v>
+      </c>
+      <c r="E66" s="3">
         <v>18305100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>17380000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>16709600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>14735500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>14960500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>15542600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>16446100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>18253600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>16645600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>14338500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>14724400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>13306100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>13862400</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3074,8 +3235,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3118,8 +3280,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3162,8 +3327,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3206,8 +3374,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3250,52 +3421,58 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3454100</v>
+      </c>
+      <c r="E72" s="3">
         <v>3365600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3674300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3558500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3096900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2558500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2368600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>422600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>138800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-56400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-528400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-737000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-708100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-585600</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3338,8 +3515,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3382,8 +3562,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3426,52 +3609,58 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>22047100</v>
+      </c>
+      <c r="E76" s="3">
         <v>21715300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>22204300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>22507400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>22157100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>21469200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>21267900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>19920900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>19302000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>18970800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>18695300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>17812700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>17747200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>17448900</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3514,101 +3703,110 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>88500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-308700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>115800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>461500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>538500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>189900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1946000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>283800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>195300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>472000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>102200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-88700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-102000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>98300</v>
       </c>
     </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3625,52 +3823,56 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>44100</v>
+      </c>
+      <c r="E83" s="3">
         <v>40600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>38700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>39500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>38500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>36300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>44100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>40700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>39300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>37600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>20700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>32900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>33600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>27900</v>
       </c>
     </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3713,8 +3915,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3757,8 +3962,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3801,8 +4009,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3845,8 +4056,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3889,52 +4103,58 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1019800</v>
+      </c>
+      <c r="E89" s="3">
         <v>965600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>621000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1451100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>374300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>133300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>13800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>684800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>519400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>489400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-797900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>491200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>113300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>294400</v>
       </c>
     </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3951,52 +4171,56 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-53200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-30600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-41200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-50600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-31300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-31900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-27000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-56600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-38400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-32000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-51700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-37700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-29500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-32300</v>
       </c>
     </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4039,8 +4263,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4083,52 +4310,58 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-306400</v>
+      </c>
+      <c r="E94" s="3">
         <v>300000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2130100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1100700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-485800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>914700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-323200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>105700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-175000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>1042400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>278200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-173900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-45000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>623900</v>
       </c>
     </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4145,8 +4378,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4189,8 +4423,11 @@
       <c r="P96" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4233,8 +4470,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4277,8 +4517,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4321,136 +4564,148 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1356700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-251900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>39800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1466600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-907800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1211600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>707600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>71700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1140900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>32400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>800400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-319600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-711900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-9100</v>
       </c>
     </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>72700</v>
+      </c>
+      <c r="E101" s="3">
         <v>22200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-102100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>53400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-41800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>57600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-35400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>5900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>56600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-59500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-34500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-643300</v>
+      </c>
+      <c r="E102" s="3">
         <v>1013200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1463800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1802500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-946600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-141300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>296100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>915600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1487300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1522400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>338400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-37700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-637700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>910300</v>
       </c>
     </row>
